--- a/artfynd/A 18115-2024 artfynd.xlsx
+++ b/artfynd/A 18115-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>117766628</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18115-2024 artfynd.xlsx
+++ b/artfynd/A 18115-2024 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796469</v>
+        <v>119796470</v>
       </c>
       <c r="B6" t="n">
-        <v>96868</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480361</v>
+        <v>480146</v>
       </c>
       <c r="R6" t="n">
-        <v>6857990</v>
+        <v>6858170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796470</v>
+        <v>119796469</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>96868</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480146</v>
+        <v>480361</v>
       </c>
       <c r="R7" t="n">
-        <v>6858170</v>
+        <v>6857990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 18115-2024 artfynd.xlsx
+++ b/artfynd/A 18115-2024 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796470</v>
+        <v>119796469</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>96868</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480146</v>
+        <v>480361</v>
       </c>
       <c r="R6" t="n">
-        <v>6858170</v>
+        <v>6857990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796469</v>
+        <v>119796470</v>
       </c>
       <c r="B7" t="n">
-        <v>96868</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480361</v>
+        <v>480146</v>
       </c>
       <c r="R7" t="n">
-        <v>6857990</v>
+        <v>6858170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 18115-2024 artfynd.xlsx
+++ b/artfynd/A 18115-2024 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>119796469</v>
       </c>
       <c r="B6" t="n">
-        <v>96868</v>
+        <v>96891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>119796470</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
